--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF0456C-FF90-DD43-A61C-0DFA12F13A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFB625A-F490-8C4C-8EB5-2E4BD3AC49B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="2780" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>italia</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1521,10 +1539,10 @@
     </row>
     <row r="35" spans="1:9" ht="21">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>68</v>
@@ -1550,10 +1568,10 @@
     </row>
     <row r="36" spans="1:9" ht="21">
       <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>73</v>
@@ -1579,186 +1597,186 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38">
-        <v>47</v>
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2.4</v>
+        <v>33</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B41">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2.4</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50">
         <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52">
-        <v>160</v>
+        <v>46</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B53">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>49</v>
+      </c>
+      <c r="B55">
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="B56">
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>58</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>59</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>102</v>
+        <v>56</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>102</v>
@@ -1766,30 +1784,54 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66">
-        <v>3299</v>
+        <v>60</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>64</v>
-      </c>
-      <c r="B67">
-        <v>4999</v>
+        <v>61</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
+        <v>63</v>
+      </c>
+      <c r="B69">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
         <v>66</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFB625A-F490-8C4C-8EB5-2E4BD3AC49B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444FE77F-67CD-5644-93EE-88CFC3C814FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444FE77F-67CD-5644-93EE-88CFC3C814FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8023D913-E989-6D47-8C3A-506B7F25614D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -425,12 +425,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,17 +1281,29 @@
       <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>1018</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1013</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1019</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1028</v>
+      <c r="C20" s="5">
+        <f>SQRT(C15^2-C16^2) + SQRT(C14^2-C16^2)</f>
+        <v>1002.8602000929095</v>
+      </c>
+      <c r="D20" s="5">
+        <f t="shared" ref="D20:H20" si="0">SQRT(D15^2-D16^2) + SQRT(D14^2-D16^2)</f>
+        <v>1017.9834093917128</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>1012.943024540129</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="0"/>
+        <v>1018.6035145287932</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="0"/>
+        <v>1029.2776225466982</v>
+      </c>
+      <c r="H20" s="5">
+        <f t="shared" si="0"/>
+        <v>1049.4124242471098</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>86</v>
@@ -1446,19 +1459,19 @@
         <v>158.5</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31:F31" si="0">AVERAGE(E33,D34)</f>
+        <f t="shared" ref="E31:F31" si="1">AVERAGE(E33,D34)</f>
         <v>169.5</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>178</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="1">AVERAGE(G33,F34)</f>
+        <f t="shared" ref="G31" si="2">AVERAGE(G33,F34)</f>
         <v>184.5</v>
       </c>
       <c r="H31">
-        <f t="shared" ref="H31" si="2">AVERAGE(H33,G34)</f>
+        <f t="shared" ref="H31" si="3">AVERAGE(H33,G34)</f>
         <v>193.5</v>
       </c>
     </row>
@@ -1471,19 +1484,19 @@
         <v>158.5</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:E32" si="3">E31</f>
+        <f t="shared" ref="D32:E32" si="4">E31</f>
         <v>169.5</v>
       </c>
       <c r="E32">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>178</v>
       </c>
       <c r="F32">
-        <f t="shared" ref="F32:G32" si="4">F34</f>
+        <f t="shared" ref="F32:G32" si="5">F34</f>
         <v>186</v>
       </c>
       <c r="G32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>195</v>
       </c>
       <c r="H32">

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8023D913-E989-6D47-8C3A-506B7F25614D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FB61BE-4330-AD4B-8C10-F1204788C42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -326,12 +326,6 @@
     <t>Road Headtube</t>
   </si>
   <si>
-    <t>Racemax Integrale</t>
-  </si>
-  <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>frame_weight</t>
   </si>
   <si>
@@ -375,6 +369,18 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>Racemax</t>
+  </si>
+  <si>
+    <t>https://us.3t.bike/cdn/shop/files/Racemax_Integrale_WPNT_GRX_1x12_700c_Avorio_DS_900x.jpg?v=1731423845</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>integrated</t>
   </si>
 </sst>
 </file>
@@ -747,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -771,7 +777,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -779,10 +790,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21">
@@ -934,7 +945,7 @@
         <v>230</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="3">
         <v>147</v>
@@ -1180,7 +1191,7 @@
         <v>582</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K17" s="3">
         <v>1018</v>
@@ -1338,7 +1349,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24">
         <v>990</v>
@@ -1552,10 +1563,10 @@
     </row>
     <row r="35" spans="1:9" ht="21">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>68</v>
@@ -1581,10 +1592,10 @@
     </row>
     <row r="36" spans="1:9" ht="21">
       <c r="A36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>73</v>
@@ -1610,10 +1621,10 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1677,18 +1688,24 @@
       <c r="A47" t="s">
         <v>41</v>
       </c>
+      <c r="B47">
+        <v>142</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
         <v>42</v>
       </c>
+      <c r="B48">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1722,7 +1739,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1750,6 +1767,9 @@
       <c r="A58" t="s">
         <v>52</v>
       </c>
+      <c r="B58" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
@@ -1792,7 +1812,7 @@
         <v>59</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1800,7 +1820,7 @@
         <v>60</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1808,7 +1828,7 @@
         <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1816,7 +1836,7 @@
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1845,7 +1865,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FB61BE-4330-AD4B-8C10-F1204788C42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F493890-6C67-6846-8A11-64DB7EA5331D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>integrated</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Bergamo, Italy</t>
   </si>
 </sst>
 </file>
@@ -734,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1868,6 +1874,14 @@
         <v>114</v>
       </c>
     </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" t="s">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F493890-6C67-6846-8A11-64DB7EA5331D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD5001-7C3C-FA4B-9780-6BE3CCF6ADFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -1781,6 +1781,9 @@
       <c r="A59" t="s">
         <v>53</v>
       </c>
+      <c r="B59" s="1" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFD5001-7C3C-FA4B-9780-6BE3CCF6ADFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB70FCC-5996-3543-AF42-F94868FD69D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,24 @@
   </si>
   <si>
     <t>Bergamo, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -740,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1708,117 +1726,108 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53">
-        <v>44</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55">
-        <v>160</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B61">
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>100</v>
@@ -1826,62 +1835,101 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>100</v>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>3299</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>4999</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>4999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>116</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/gravel/3T Racemax Integrale 2025.xlsx
+++ b/data/gravel/3T Racemax Integrale 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB70FCC-5996-3543-AF42-F94868FD69D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4D4F8F-40A4-3F47-9562-A8842A0739EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1486,28 +1486,22 @@
         <v>27</v>
       </c>
       <c r="C31">
-        <f>C33</f>
         <v>145</v>
       </c>
       <c r="D31">
-        <f>AVERAGE(D33,C34)</f>
-        <v>158.5</v>
+        <v>157</v>
       </c>
       <c r="E31">
-        <f t="shared" ref="E31:F31" si="1">AVERAGE(E33,D34)</f>
-        <v>169.5</v>
+        <v>168</v>
       </c>
       <c r="F31">
-        <f t="shared" si="1"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G31">
-        <f t="shared" ref="G31" si="2">AVERAGE(G33,F34)</f>
-        <v>184.5</v>
+        <v>183</v>
       </c>
       <c r="H31">
-        <f t="shared" ref="H31" si="3">AVERAGE(H33,G34)</f>
-        <v>193.5</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1515,132 +1509,90 @@
         <v>28</v>
       </c>
       <c r="C32">
-        <f>D31</f>
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:E32" si="4">E31</f>
-        <v>169.5</v>
+        <v>171</v>
       </c>
       <c r="E32">
-        <f t="shared" si="4"/>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F32">
-        <f t="shared" ref="F32:G32" si="5">F34</f>
         <v>186</v>
       </c>
       <c r="G32">
-        <f t="shared" si="5"/>
         <v>195</v>
       </c>
       <c r="H32">
-        <f>H34</f>
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="C33">
-        <v>145</v>
-      </c>
-      <c r="D33">
-        <v>157</v>
-      </c>
-      <c r="E33">
-        <v>168</v>
-      </c>
-      <c r="F33">
-        <v>176</v>
-      </c>
-      <c r="G33">
-        <v>183</v>
-      </c>
-      <c r="H33">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+    <row r="33" spans="1:9" ht="21">
+      <c r="C33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="21">
       <c r="A34" t="s">
         <v>29</v>
       </c>
       <c r="B34" t="s">
         <v>30</v>
       </c>
-      <c r="C34">
-        <v>160</v>
-      </c>
-      <c r="D34">
-        <v>171</v>
-      </c>
-      <c r="E34">
-        <v>180</v>
-      </c>
-      <c r="F34">
-        <v>186</v>
-      </c>
-      <c r="G34">
-        <v>195</v>
-      </c>
-      <c r="H34">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="21">
+      <c r="C34" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" t="s">
         <v>106</v>
       </c>
       <c r="B35" t="s">
         <v>107</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H35" t="s">
-        <v>72</v>
-      </c>
-      <c r="I35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="21">
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" t="s">
         <v>108</v>
       </c>
       <c r="B36" t="s">
         <v>109</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H36" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:9">
